--- a/剧本创作平台架构TodoList.xlsx
+++ b/剧本创作平台架构TodoList.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,14 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <color rgb="009C5700"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -90,8 +96,32 @@
         <fgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+        <bgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -113,11 +143,55 @@
         <color rgb="00D1D5DB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -165,6 +239,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -587,6 +675,12 @@
           <t>一、用户与账号体系（贯穿全局）</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="18" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -609,7 +703,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -646,7 +740,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -683,7 +777,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -720,7 +814,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -742,6 +836,12 @@
           <t>二、剧本列表页（我的剧本）</t>
         </is>
       </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="18" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -764,9 +864,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -776,7 +876,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>GET /api/scripts 需加 q=关键词 搜索（title LIKE）</t>
+          <t>GET /api/scripts 支持 q/status/path_type/tag/archived/page/page_size</t>
         </is>
       </c>
     </row>
@@ -801,9 +901,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -813,7 +913,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>需保存初始 config（四维标签/体量/节奏等元信息）</t>
+          <t>POST /api/scripts 创建时即保存 path_type+config（四维标签/体量/节奏等）并生成 v1 初始版本</t>
         </is>
       </c>
     </row>
@@ -838,9 +938,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E10" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -850,7 +950,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>PUT 基本字段已做，需加 archive 状态流转</t>
+          <t>PUT/PATCH 支持重命名/描述/tags/config/status/step/progress；POST restore 已实现</t>
         </is>
       </c>
     </row>
@@ -875,9 +975,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E11" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -887,7 +987,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>POST /api/scripts/{id}/duplicate</t>
+          <t>POST /api/scripts/{id}/duplicate 完整复制 content/config/tags 并生成 v1</t>
         </is>
       </c>
     </row>
@@ -912,9 +1012,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
@@ -924,7 +1024,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>当前硬删，建议改为软删加 deleted_at 字段</t>
+          <t>软删已实现（deleted_at + ?permanent=true 永久删除；POST restore 恢复）</t>
         </is>
       </c>
     </row>
@@ -949,9 +1049,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -961,7 +1061,7 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>加 cover_url/progress/step/tags/config/deleted_at 字段</t>
+          <t>scripts 表已包含 cover_url/progress/step/tags/config/deleted_at/current_version_id/locked_at</t>
         </is>
       </c>
     </row>
@@ -986,7 +1086,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1008,6 +1108,12 @@
           <t>三、Step 0 创作入口 — AI 原创路径</t>
         </is>
       </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="18" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -1030,9 +1136,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -1042,7 +1148,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>GET /api/tags?category=xxx，词库从数据库读</t>
+          <t>GET /api/tags?category=xxx；GET /api/tags/categories 拉取分类；从 tag_dictionaries 读</t>
         </is>
       </c>
     </row>
@@ -1067,9 +1173,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -1079,7 +1185,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>id/category/name/weight/sort_order/is_active，支持运营维护</t>
+          <t>tag_dictionaries 表已建；seed.py 初始化 7 类标签（题材/情节/时空/情绪/画风/镜头/外貌）</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1210,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1141,9 +1247,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F19" s="14" t="inlineStr">
@@ -1153,7 +1259,7 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>核心能力，入参：四维标签+风格+体量+节奏+必含/避雷+提示词；流式返回16个大纲模块</t>
+          <t>POST /api/ai/outline/generate SSE+Mock 已就位，待接入真实大模型</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1284,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1215,9 +1321,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E21" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -1227,7 +1333,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>ai_tasks 表记录 pending/streaming/done/failed，SSE 中断可重连</t>
+          <t>ai_tasks 表+status/progress/params/result_ref/error_msg/timestamps 已建；断线重连查询待完善</t>
         </is>
       </c>
     </row>
@@ -1252,9 +1358,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F22" s="14" t="inlineStr">
@@ -1264,7 +1370,7 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>tags/style/pace/must/avoid/novels 等便于复用和审计</t>
+          <t>scripts.config JSON 字段保存四维标签/风格/体量/节奏/must/avoid 快照</t>
         </is>
       </c>
     </row>
@@ -1274,6 +1380,12 @@
           <t>四、Step 0 创作入口 — 导入剧本路径</t>
         </is>
       </c>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="18" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -1296,9 +1408,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -1308,7 +1420,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>python-docx 解析 docx、pdfplumber 解析 pdf</t>
+          <t>POST /api/scripts/{id}/imports 支持 txt 文本入库；docx/pdf 解析待做</t>
         </is>
       </c>
     </row>
@@ -1333,9 +1445,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -1345,7 +1457,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>喂入原文+目标集数+情绪基调，返回 outlineData+episodes 骨架</t>
+          <t>POST /api/ai/import/parse SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1370,9 +1482,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E26" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -1382,7 +1494,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>id/script_id/file_name/file_type/raw_text/created_at</t>
+          <t>script_imports 表（id/script_id/file_name/file_type/file_size/file_url/raw_text/created_at）已建</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1519,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1429,6 +1541,12 @@
           <t>五、Step 1 大纲审核与修改</t>
         </is>
       </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="18" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -1451,9 +1569,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E29" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F29" s="10" t="inlineStr">
@@ -1463,7 +1581,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>PUT 整包已做，建议加 PATCH 局部更新减流量</t>
+          <t>PATCH /api/scripts/{id} 已实现（model_dump(exclude_unset=True) 字段级合并）</t>
         </is>
       </c>
     </row>
@@ -1488,9 +1606,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
@@ -1500,7 +1618,7 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>入参 outlineData，流式返回每个模块的 issues+aiScore+tone</t>
+          <t>POST /api/ai/outline/review SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1525,9 +1643,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -1537,7 +1655,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>入参：单模块+勾选 issues+用户 note，流式返回修改后内容</t>
+          <t>POST /api/ai/outline/modify-module SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1562,9 +1680,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E32" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -1574,7 +1692,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>入参：多模块+globalNote，流式返回批量修改结果</t>
+          <t>POST /api/ai/outline/batch-modify SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1717,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1636,7 +1754,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1673,9 +1791,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -1685,7 +1803,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>复用 PATCH content</t>
+          <t>PATCH /api/scripts/{id} 支持任意字段（含 outlineData 全文）更新</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1828,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1732,6 +1850,12 @@
           <t>六、Step 2 人物小传</t>
         </is>
       </c>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="18" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="13" t="inlineStr">
@@ -1754,9 +1878,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
@@ -1766,7 +1890,7 @@
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>POST/GET/PUT/DELETE /api/scripts/{id}/characters/{cid}</t>
+          <t>POST/GET/PUT/DELETE /api/scripts/{id}/characters/{cid} 已实现（存 content.characters JSON 数组）</t>
         </is>
       </c>
     </row>
@@ -1791,9 +1915,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F39" s="14" t="inlineStr">
@@ -1803,7 +1927,7 @@
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>推荐初期 JSON，跨剧本复用再拆表</t>
+          <t>决策落地：初期采用 JSON 数组（content.characters），不独立建表，跨剧本复用再拆</t>
         </is>
       </c>
     </row>
@@ -1828,9 +1952,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -1840,7 +1964,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>复用 tag_dictionaries 的 appearance 分类</t>
+          <t>复用 tag_dictionaries 表 appearance 分类标签</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1989,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -1902,9 +2026,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E42" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -1914,7 +2038,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>检查动机冲突、人设矛盾、与大纲冲突，返回 issues</t>
+          <t>POST /api/ai/characters/review SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1939,9 +2063,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E43" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -1951,7 +2075,7 @@
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>根据大纲和主角自动生成配角/反派小传</t>
+          <t>POST /api/ai/characters/generate SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -1976,7 +2100,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2013,7 +2137,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2035,6 +2159,12 @@
           <t>七、Step 3 分集剧本（核心产出）</t>
         </is>
       </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="18" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="13" t="inlineStr">
@@ -2057,9 +2187,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -2069,7 +2199,7 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>最核心，4层结构 Episode→Storyboard→Camera→Behavior，遵守节奏规则</t>
+          <t>POST /api/ai/episode/generate SSE+Mock 已就位（4层结构 Episode→SB→Camera→Behavior）</t>
         </is>
       </c>
     </row>
@@ -2094,9 +2224,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -2106,7 +2236,7 @@
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>检查 plot/logic/character/continuity/timing，返回 T0/T1/T2 issues</t>
+          <t>POST /api/ai/episode/review SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -2131,9 +2261,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F49" s="14" t="inlineStr">
@@ -2143,7 +2273,7 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>按勾选 issues 修改对应 behaviors，保留其他不变</t>
+          <t>POST /api/ai/episode/fix SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -2168,9 +2298,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -2180,7 +2310,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>选中段落+改写指令，返回多个候选版本</t>
+          <t>POST /api/ai/episode/rewrite-segment SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -2205,9 +2335,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -2217,7 +2347,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>POST/GET/PUT/DELETE /api/scripts/{id}/episodes/{eid}</t>
+          <t>POST/GET/PUT/DELETE /api/scripts/{id}/episodes/{eid} 已实现（存 content.episodes）</t>
         </is>
       </c>
     </row>
@@ -2242,9 +2372,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E52" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -2254,7 +2384,7 @@
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>前端算+AI生成时后端二次校验</t>
+          <t>前端即时计算 + 后端 POST /episodes/{eid}/validate 二次校验（递归累加 behaviors.duration 与 ep.duration 严格相等）</t>
         </is>
       </c>
     </row>
@@ -2279,9 +2409,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -2291,7 +2421,7 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>episodes[i].locked=true，锁定后AI不再修改</t>
+          <t>POST /episodes/{eid}/pass 设 passed=true+passed_at+passedEpisodes 索引；GET /passed/all 聚合；POST unpass 取消</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2446,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E54" s="22" t="inlineStr">
         <is>
           <t>无需</t>
         </is>
@@ -2353,7 +2483,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2375,6 +2505,12 @@
           <t>八、版本管理（贯穿 Step1-3）</t>
         </is>
       </c>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="18" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -2397,7 +2533,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -2434,9 +2570,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E58" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -2446,7 +2582,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>JSON 递归 diff，返回字段级修改点</t>
+          <t>GET /api/scripts/{id}/versions/diff?v1=&amp;v2= 实现递归 JSON diff（_ADDED/_REMOVED/_CHANGED）</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2607,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2508,9 +2644,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E60" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -2520,7 +2656,7 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>加 is_final/is_locked 字段+locked_at，定稿后不可编辑（可解锁）</t>
+          <t>ScriptVersion.is_final + POST lock（存版本快照+locked_at）+ unlock 已实现；定稿权限细节待细化</t>
         </is>
       </c>
     </row>
@@ -2545,9 +2681,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E61" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -2557,7 +2693,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>python-docx/reportlab 生成专业剧本格式</t>
+          <t>GET /export?format=json|txt 已实现；docx/pdf/fountain 待做（python-docx/reportlab）</t>
         </is>
       </c>
     </row>
@@ -2567,6 +2703,12 @@
           <t>九、AI 基础设施（所有 AI 接口的支撑层）</t>
         </is>
       </c>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="F62" s="17" t="n"/>
+      <c r="G62" s="18" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="13" t="inlineStr">
@@ -2589,9 +2731,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E63" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E63" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -2601,7 +2743,7 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>封装 OpenAI/Claude/豆包/通义/DeepSeek，统一 chat() 接口</t>
+          <t>AiProvider 抽象层 + MockProvider 已建；真实多模型（OpenAI/Claude/豆包/通义/DeepSeek）统一 chat() 待接入</t>
         </is>
       </c>
     </row>
@@ -2626,9 +2768,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E64" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E64" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -2638,7 +2780,7 @@
       </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>api_key/model/base_url/is_active，支持运营切换</t>
+          <t>ai_providers 表已建（name/provider/model_name/base_url/api_key_enc/task_bindings/is_active/priority）；Mock Provider 已 seed</t>
         </is>
       </c>
     </row>
@@ -2663,9 +2805,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E65" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E65" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F65" s="14" t="inlineStr">
@@ -2675,7 +2817,7 @@
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>prompt_templates 表，每类任务绑定模板版本</t>
+          <t>prompt_templates 表已建（task_key/version/system_prompt/user_prompt_template/variables）；11 类任务模板已 seed</t>
         </is>
       </c>
     </row>
@@ -2700,9 +2842,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E66" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E66" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -2712,7 +2854,7 @@
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>记录 tokens/latency/status/error，计费+排查必备</t>
+          <t>ai_calls 表已建（BIGINT id/user_id/script_id/version_id/task_key/provider_id/model_name/input_tokens/output_tokens/latency_ms/status/error_msg/request_body/created_at）</t>
         </is>
       </c>
     </row>
@@ -2737,9 +2879,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E67" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F67" s="14" t="inlineStr">
@@ -2749,7 +2891,7 @@
       </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
-          <t>FastAPI StreamingResponse，前端打字机效果</t>
+          <t>SSE 基础设施已建（StreamingResponse+text/event-stream+Cache-Control/Connection/X-Accel-Buffering 头）</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2916,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E68" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2811,7 +2953,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E69" s="14" t="inlineStr">
+      <c r="E69" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2848,7 +2990,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2870,6 +3012,12 @@
           <t>十、存储与基建</t>
         </is>
       </c>
+      <c r="B71" s="17" t="n"/>
+      <c r="C71" s="17" t="n"/>
+      <c r="D71" s="17" t="n"/>
+      <c r="E71" s="17" t="n"/>
+      <c r="F71" s="17" t="n"/>
+      <c r="G71" s="18" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="5" t="inlineStr">
@@ -2892,7 +3040,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2929,7 +3077,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -2966,7 +3114,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3003,7 +3151,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3040,7 +3188,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3077,7 +3225,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3099,6 +3247,12 @@
           <t>十一、前端对接层改造</t>
         </is>
       </c>
+      <c r="B78" s="17" t="n"/>
+      <c r="C78" s="17" t="n"/>
+      <c r="D78" s="17" t="n"/>
+      <c r="E78" s="17" t="n"/>
+      <c r="F78" s="17" t="n"/>
+      <c r="G78" s="18" t="n"/>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="13" t="inlineStr">
@@ -3121,7 +3275,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E79" s="14" t="inlineStr">
+      <c r="E79" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3158,7 +3312,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E80" s="14" t="inlineStr">
+      <c r="E80" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3195,7 +3349,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E81" s="14" t="inlineStr">
+      <c r="E81" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3232,7 +3386,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E82" s="14" t="inlineStr">
+      <c r="E82" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3269,7 +3423,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3306,7 +3460,7 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -3390,6 +3544,10 @@
           <t>users（用户表 ✅已建）</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="18" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -3617,6 +3775,10 @@
           <t>scripts（剧本表 ✅已建，需扩展）</t>
         </is>
       </c>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="18" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
@@ -3990,6 +4152,10 @@
           <t>script_versions（版本快照表 ✅已建）</t>
         </is>
       </c>
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="18" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
@@ -4209,6 +4375,10 @@
           <t>script_imports（导入原文表 🆕待建）</t>
         </is>
       </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="18" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -4380,6 +4550,10 @@
           <t>tag_dictionaries（标签词典表 🆕待建）</t>
         </is>
       </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="18" t="n"/>
     </row>
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="15" t="inlineStr">
@@ -4529,6 +4703,10 @@
           <t>ai_providers（AI 模型配置表 🆕待建）</t>
         </is>
       </c>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="18" t="n"/>
     </row>
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="15" t="inlineStr">
@@ -4726,6 +4904,10 @@
           <t>prompt_templates（Prompt 模板表 🆕待建）</t>
         </is>
       </c>
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="18" t="n"/>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="15" t="inlineStr">
@@ -4911,6 +5093,10 @@
           <t>ai_calls（AI 调用日志表 🆕待建）</t>
         </is>
       </c>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="18" t="n"/>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="15" t="inlineStr">
@@ -5190,6 +5376,10 @@
           <t>ai_tasks（AI 任务队列表 🆕待建）</t>
         </is>
       </c>
+      <c r="B94" s="17" t="n"/>
+      <c r="C94" s="17" t="n"/>
+      <c r="D94" s="17" t="n"/>
+      <c r="E94" s="18" t="n"/>
     </row>
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="15" t="inlineStr">
@@ -5429,6 +5619,10 @@
           <t>character_references（角色参考图表 🆕待建，可选）</t>
         </is>
       </c>
+      <c r="B107" s="17" t="n"/>
+      <c r="C107" s="17" t="n"/>
+      <c r="D107" s="17" t="n"/>
+      <c r="E107" s="18" t="n"/>
     </row>
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="15" t="inlineStr">
@@ -5624,6 +5818,12 @@
           <t>认证 Auth</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n"/>
+      <c r="G2" s="18" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -5646,7 +5846,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -5683,7 +5883,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -5720,7 +5920,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -5753,7 +5953,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -5786,7 +5986,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -5808,6 +6008,12 @@
           <t>剧本 Scripts</t>
         </is>
       </c>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="18" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -5830,9 +6036,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E9" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
@@ -5842,7 +6048,7 @@
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>加 q/status 参数</t>
+          <t>已支持 q/status/path_type/tag/archived/page/page_size</t>
         </is>
       </c>
     </row>
@@ -5867,7 +6073,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -5904,7 +6110,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -5941,9 +6147,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E12" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -5953,7 +6159,7 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>只传变更字段</t>
+          <t>PATCH 局部更新已实现（exclude_unset=True 字段合并），PUT 为 alias</t>
         </is>
       </c>
     </row>
@@ -5978,9 +6184,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>部分完成</t>
+      <c r="E13" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
@@ -5990,7 +6196,7 @@
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>改软删</t>
+          <t>软删（deleted_at）+ ?permanent=true 永久删；POST /{id}/restore 恢复</t>
         </is>
       </c>
     </row>
@@ -6015,9 +6221,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -6027,7 +6233,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>完整复制 content</t>
+          <t>完整复制 content/config/tags 并生成 v1 版本</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6258,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -6085,9 +6291,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
@@ -6097,7 +6303,7 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>is_final=true</t>
+          <t>保存当前版本快照+is_final+locked_at；POST unlock 兼容</t>
         </is>
       </c>
     </row>
@@ -6107,6 +6313,12 @@
           <t>版本 Versions</t>
         </is>
       </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="18" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
@@ -6129,7 +6341,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -6162,7 +6374,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -6199,7 +6411,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -6232,7 +6444,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -6269,7 +6481,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -6306,9 +6518,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E23" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -6318,7 +6530,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>v1/v2 参数，返回 JSON diff</t>
+          <t>v1/v2 参数，返回递归 JSON diff（_ADDED/_REMOVED/_CHANGED）</t>
         </is>
       </c>
     </row>
@@ -6328,6 +6540,12 @@
           <t>标签与词库 Tags</t>
         </is>
       </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="18" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
@@ -6350,9 +6568,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -6362,7 +6580,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>按 category 过滤</t>
+          <t>按 category 过滤；另有 /api/tags/categories 返回分类列表</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6605,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -6420,7 +6638,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -6453,7 +6671,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -6471,6 +6689,12 @@
           <t>导入 Import</t>
         </is>
       </c>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="18" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -6493,9 +6717,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E30" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -6505,7 +6729,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>multipart，支持 txt/docx/pdf</t>
+          <t>当前为 POST /api/scripts/{id}/imports 支持 txt 文本入库；docx/pdf 待做</t>
         </is>
       </c>
     </row>
@@ -6530,9 +6754,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E31" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -6542,7 +6766,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>SSE 流式，返回 outline+episodes</t>
+          <t>路径为 POST /api/ai/import/parse；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -6552,6 +6776,12 @@
           <t>角色 Characters</t>
         </is>
       </c>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="18" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="13" t="inlineStr">
@@ -6574,9 +6804,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -6586,7 +6816,7 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>可从 content JSON 派生</t>
+          <t>返回 content.characters</t>
         </is>
       </c>
     </row>
@@ -6611,9 +6841,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
@@ -6621,7 +6851,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr"/>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>id 自增 c1/c2...，支持任意自定义字段透传</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
@@ -6644,9 +6878,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F35" s="14" t="inlineStr">
@@ -6654,7 +6888,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>字段合并更新，禁止改 id</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="13" t="inlineStr">
@@ -6677,9 +6915,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -6687,7 +6925,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr"/>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>从 content.characters 移除</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
@@ -6710,7 +6952,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -6728,6 +6970,12 @@
           <t>分集 Episodes</t>
         </is>
       </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="18" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -6750,9 +6998,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -6760,7 +7008,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G39" s="12" t="inlineStr"/>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>返回 content.episodes</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -6783,9 +7035,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -6793,7 +7045,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr"/>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>duration 默认取 config.ep_duration(90)；自动分配 id</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
@@ -6816,9 +7072,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -6826,7 +7082,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G41" s="12" t="inlineStr"/>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>支持 storyboards/cameras/behaviors 嵌套更新</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -6849,9 +7109,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -6859,7 +7119,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G42" s="12" t="inlineStr"/>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>同步清理 content.passedEpisodes 记录</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
@@ -6882,9 +7146,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F43" s="14" t="inlineStr">
@@ -6894,7 +7158,7 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>locked=true</t>
+          <t>时长未通过返回 409；?force=true 强制通过；POST /{eid}/unpass 取消；GET /passed/all 聚合</t>
         </is>
       </c>
     </row>
@@ -6919,9 +7183,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -6929,7 +7193,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>返回 expected_duration/actual_duration/diff/issues</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -6937,6 +7205,12 @@
           <t>AI 核心接口（均为 SSE 流式）</t>
         </is>
       </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="18" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
@@ -6959,9 +7233,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E46" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
@@ -6971,7 +7245,7 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>流式返回 16 个大纲模块</t>
+          <t>路径为 POST /api/ai/outline/generate；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -6996,9 +7270,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E47" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F47" s="14" t="inlineStr">
@@ -7008,7 +7282,7 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>返回 issues+aiScore</t>
+          <t>路径为 POST /api/ai/outline/review；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7033,9 +7307,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E48" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -7045,7 +7319,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>流式</t>
+          <t>路径为 POST /api/ai/outline/modify-module；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7070,9 +7344,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -7082,7 +7356,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>流式</t>
+          <t>路径为 POST /api/ai/outline/batch-modify；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7107,9 +7381,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E50" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -7119,7 +7393,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>返回人物 issues</t>
+          <t>路径为 POST /api/ai/characters/review；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7144,9 +7418,9 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E51" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
@@ -7156,7 +7430,7 @@
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>流式</t>
+          <t>路径为 POST /api/ai/characters/generate；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7181,9 +7455,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E52" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -7193,7 +7467,7 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>流式返回4层结构</t>
+          <t>路径为 POST /api/ai/episode/generate；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7218,9 +7492,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E53" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F53" s="14" t="inlineStr">
@@ -7230,7 +7504,7 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>返回 T0/T1/T2 issues</t>
+          <t>路径为 POST /api/ai/episode/review；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7255,9 +7529,9 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E54" s="14" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E54" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -7267,7 +7541,7 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>按 issues 修改对应 behaviors</t>
+          <t>路径为 POST /api/ai/episode/fix；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7292,9 +7566,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E55" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -7304,7 +7578,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>返回多候选</t>
+          <t>路径为 POST /api/ai/episode/rewrite-segment；SSE+Mock 已就位</t>
         </is>
       </c>
     </row>
@@ -7314,6 +7588,12 @@
           <t>导出 Export</t>
         </is>
       </c>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="18" t="n"/>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="11" t="inlineStr">
@@ -7336,9 +7616,9 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>待做</t>
+      <c r="E57" s="20" t="inlineStr">
+        <is>
+          <t>部分完成</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -7348,7 +7628,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>format=docx|pdf|txt|fountain</t>
+          <t>format=json/txt 已实现；docx/pdf/fountain 待做</t>
         </is>
       </c>
     </row>
@@ -7358,6 +7638,12 @@
           <t>任务与上传</t>
         </is>
       </c>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="17" t="n"/>
+      <c r="G58" s="18" t="n"/>
     </row>
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
@@ -7380,7 +7666,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -7417,7 +7703,7 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -7450,7 +7736,7 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
@@ -7487,7 +7773,7 @@
           <t>P0</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
+      <c r="E62" s="19" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
@@ -7560,6 +7846,9 @@
           <t>scripts.content 根对象</t>
         </is>
       </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="18" t="n"/>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -7721,6 +8010,9 @@
           <t>OutlineModule 大纲模块</t>
         </is>
       </c>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="18" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
@@ -7948,6 +8240,9 @@
           <t>OutlineIssue 大纲问题</t>
         </is>
       </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="18" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
@@ -8043,6 +8338,9 @@
           <t>Character 角色</t>
         </is>
       </c>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="15" t="inlineStr">
@@ -8380,6 +8678,9 @@
           <t>Episode 分集</t>
         </is>
       </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="18" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="15" t="inlineStr">
@@ -8519,6 +8820,9 @@
           <t>Storyboard 分镜 → Camera 镜头 → Behavior 行为（4 层嵌套）</t>
         </is>
       </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="18" t="n"/>
     </row>
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="15" t="inlineStr">
@@ -8834,6 +9138,9 @@
           <t>EpisodeIssue 分集 AI 问题</t>
         </is>
       </c>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="18" t="n"/>
     </row>
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="15" t="inlineStr">
@@ -8991,6 +9298,9 @@
           <t>scripts.config 创作配置对象</t>
         </is>
       </c>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="18" t="n"/>
     </row>
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="15" t="inlineStr">

--- a/剧本创作平台架构TodoList.xlsx
+++ b/剧本创作平台架构TodoList.xlsx
@@ -620,7 +620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E63" s="20" t="inlineStr">
         <is>
-          <t>部分完成</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="F63" s="14" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
-          <t>AiProvider 抽象层 + MockProvider 已建；真实多模型（OpenAI/Claude/豆包/通义/DeepSeek）统一 chat() 待接入</t>
+          <t>LLMProvider 已接入真实大模型（OpenAI 兼容协议，覆盖 DeepSeek/豆包/Qwen/智谱/Moonshot/Ollama/vLLM/one-api 等）；httpx 异步 SSE 流式 + response_format=json_object + 稳健 JSON 提取；AiService 支持按 name/task_key/wildcard/config 四级路由，自动降级到 Mock；已 E2E 验证</t>
         </is>
       </c>
     </row>
@@ -3007,69 +3007,69 @@
       </c>
     </row>
     <row r="71" ht="26" customHeight="1">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>AI Provider 模型管理 CRUD API</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>后端 API</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E71" s="21" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>AI 基建</t>
+        </is>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>GET/POST/PUT/DELETE /api/ai-providers + /activate /bindings /set-default /test 全套 CRUD；api_key 脱敏返回（前6+****+后4）；task_bindings 校验；/test 真正请求 base_url/chat/completions 联通测试；mock 内置 provider 不可删；已 curl 端到端验证</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="32" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>十、存储与基建</t>
         </is>
       </c>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="17" t="n"/>
-      <c r="E71" s="17" t="n"/>
-      <c r="F71" s="17" t="n"/>
-      <c r="G71" s="18" t="n"/>
-    </row>
-    <row r="72" ht="32" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>9.1</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>对象存储（封面/参考图/导入文件）</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>存储</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="E72" s="21" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>基建</t>
-        </is>
-      </c>
-      <c r="G72" s="6" t="inlineStr">
-        <is>
-          <t>本地 /static/uploads 起步，后切 MinIO/OSS/COS</t>
-        </is>
-      </c>
+      <c r="B72" s="17" t="n"/>
+      <c r="C72" s="17" t="n"/>
+      <c r="D72" s="17" t="n"/>
+      <c r="E72" s="17" t="n"/>
+      <c r="F72" s="17" t="n"/>
+      <c r="G72" s="18" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>向量库（RAG用）</t>
+          <t>对象存储（封面/参考图/导入文件）</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>基础设施</t>
+          <t>存储</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -3089,222 +3089,222 @@
       </c>
       <c r="G73" s="6" t="inlineStr">
         <is>
-          <t>pgvector轻/Milvus重/Chroma开发</t>
+          <t>本地 /static/uploads 起步，后切 MinIO/OSS/COS</t>
         </is>
       </c>
     </row>
     <row r="74" ht="32" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>9.2</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>向量库（RAG用）</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>基础设施</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E74" s="21" t="inlineStr">
+        <is>
+          <t>待做</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>基建</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>pgvector轻/Milvus重/Chroma开发</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>Redis（缓存/队列/SSE状态）</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>基础设施</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
+      <c r="D75" s="6" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E74" s="21" t="inlineStr">
+      <c r="E75" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>基建</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>并发上来后必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="32" customHeight="1">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>9.4</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="inlineStr">
-        <is>
-          <t>Alembic 数据库迁移</t>
-        </is>
-      </c>
-      <c r="C75" s="12" t="inlineStr">
-        <is>
-          <t>后端工程</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E75" s="21" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="F75" s="12" t="inlineStr">
-        <is>
-          <t>基建</t>
-        </is>
-      </c>
-      <c r="G75" s="12" t="inlineStr">
-        <is>
-          <t>当前 create_all，生产必须加迁移</t>
         </is>
       </c>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Alembic 数据库迁移</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>后端工程</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E76" s="21" t="inlineStr">
+        <is>
+          <t>待做</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>基建</t>
+        </is>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>当前 create_all，生产必须加迁移</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="32" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
           <t>9.5</t>
         </is>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B77" s="12" t="inlineStr">
         <is>
           <t>Docker Compose 一键启动</t>
         </is>
       </c>
-      <c r="C76" s="12" t="inlineStr">
+      <c r="C77" s="12" t="inlineStr">
         <is>
           <t>部署</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="E76" s="21" t="inlineStr">
+      <c r="E77" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
       </c>
-      <c r="F76" s="12" t="inlineStr">
+      <c r="F77" s="12" t="inlineStr">
         <is>
           <t>基建</t>
         </is>
       </c>
-      <c r="G76" s="12" t="inlineStr">
+      <c r="G77" s="12" t="inlineStr">
         <is>
           <t>mysql + redis + backend + frontend</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>9.6</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>日志监控告警</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>运维</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="E77" s="21" t="inlineStr">
+      <c r="E78" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
       </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>基建</t>
         </is>
       </c>
-      <c r="G77" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>结构化日志、慢查询、AI异常告警</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="26" customHeight="1">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79" ht="32" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>十一、前端对接层改造</t>
         </is>
       </c>
-      <c r="B78" s="17" t="n"/>
-      <c r="C78" s="17" t="n"/>
-      <c r="D78" s="17" t="n"/>
-      <c r="E78" s="17" t="n"/>
-      <c r="F78" s="17" t="n"/>
-      <c r="G78" s="18" t="n"/>
-    </row>
-    <row r="79" ht="32" customHeight="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>10.1</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>前端 API 客户端封装（JWT/错误/401）</t>
-        </is>
-      </c>
-      <c r="C79" s="14" t="inlineStr">
-        <is>
-          <t>前端改造</t>
-        </is>
-      </c>
-      <c r="D79" s="14" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="E79" s="21" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="F79" s="14" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="G79" s="14" t="inlineStr">
-        <is>
-          <t>统一 fetch 封装</t>
-        </is>
-      </c>
+      <c r="B79" s="17" t="n"/>
+      <c r="C79" s="17" t="n"/>
+      <c r="D79" s="17" t="n"/>
+      <c r="E79" s="17" t="n"/>
+      <c r="F79" s="17" t="n"/>
+      <c r="G79" s="18" t="n"/>
     </row>
     <row r="80" ht="32" customHeight="1">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>登录/注册页面</t>
+          <t>前端 API 客户端封装（JWT/错误/401）</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>前端页面</t>
+          <t>前端改造</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -3324,24 +3324,24 @@
       </c>
       <c r="G80" s="14" t="inlineStr">
         <is>
-          <t>目前前端没有</t>
+          <t>统一 fetch 封装</t>
         </is>
       </c>
     </row>
     <row r="81" ht="32" customHeight="1">
       <c r="A81" s="13" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>localStorage → API 数据迁移</t>
+          <t>登录/注册页面</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>前端改造</t>
+          <t>前端页面</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -3361,116 +3361,153 @@
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>版本、剧本列表、自动保存全部改走后端</t>
+          <t>目前前端没有</t>
         </is>
       </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="13" t="inlineStr">
         <is>
+          <t>10.3</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>localStorage → API 数据迁移</t>
+        </is>
+      </c>
+      <c r="C82" s="14" t="inlineStr">
+        <is>
+          <t>前端改造</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E82" s="21" t="inlineStr">
+        <is>
+          <t>待做</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="G82" s="14" t="inlineStr">
+        <is>
+          <t>版本、剧本列表、自动保存全部改走后端</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
           <t>10.4</t>
         </is>
       </c>
-      <c r="B82" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>SSE 流式消费（打字机效果）</t>
         </is>
       </c>
-      <c r="C82" s="14" t="inlineStr">
+      <c r="C83" s="14" t="inlineStr">
         <is>
           <t>前端改造</t>
         </is>
       </c>
-      <c r="D82" s="14" t="inlineStr">
+      <c r="D83" s="14" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="E82" s="21" t="inlineStr">
+      <c r="E83" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
       </c>
-      <c r="F82" s="14" t="inlineStr">
+      <c r="F83" s="14" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="G82" s="14" t="inlineStr">
+      <c r="G83" s="14" t="inlineStr">
         <is>
           <t>EventSource/fetch-stream</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="32" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>离线/弱网本地缓存同步</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="E83" s="21" t="inlineStr">
-        <is>
-          <t>待做</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>前端</t>
-        </is>
-      </c>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>后期加</t>
         </is>
       </c>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>离线/弱网本地缓存同步</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="E84" s="21" t="inlineStr">
+        <is>
+          <t>待做</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>后期加</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
           <t>10.6</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>前端路由系统（Vue/React Router）</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>前端架构</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="E84" s="21" t="inlineStr">
+      <c r="E85" s="21" t="inlineStr">
         <is>
           <t>待做</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F85" s="8" t="inlineStr">
         <is>
           <t>前端</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="G85" s="8" t="inlineStr">
         <is>
           <t>可选，目前不影响功能</t>
         </is>
@@ -5763,7 +5800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7784,6 +7821,352 @@
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AI Provider 模型管理</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/api/ai-providers</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>模型列表（按 priority 升序，key 脱敏）</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>返回 providers[]：id/name/provider/model_name/base_url/has_key/key_preview/task_bindings/is_active/priority/created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/api/ai-providers</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>新增模型配置</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>name 唯一；openai 类型需 base_url+api_key+model_name；task_bindings 必须为合法 task_key 或 ["*"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>获取单个模型详情</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>key 同样脱敏</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>更新模型配置（部分字段）</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>支持改 provider/model_name/base_url/api_key/task_bindings/is_active/priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>删除模型</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>内置 mock 不可删除；被引用的 provider_id 在 ai_calls 中保留日志</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}/activate</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>启用/停用模型</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>?active=true|false</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}/bindings</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>设置任务绑定</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>body: {task_bindings:[...]}；校验 task_key 合法性</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}/set-default</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>设为全局默认</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>自动设 priority=10、bindings=["*"]，其他 provider 提权到 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/api/ai-providers/{name}/test</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>连通性测试（非流式）</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>真实 ping {base_url}/chat/completions；返回 ok/model/reply/usage/error</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G62"/>
@@ -9609,7 +9992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10025,6 +10408,45 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【AI 基建备注】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LLMProvider</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>所有 AI 接口的底层引擎</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>system_prompt+user_prompt+temperature+json_mode</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>异步 httpx SSE 流式：phase→delta*→result→done/error；自动解析 usage.prompt_tokens/completion_tokens/total_tokens 写入 ai_calls</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>通过 AiService 按 task_key 路由到匹配的 provider/model</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OpenAI 兼容协议（DeepSeek/豆包/Qwen/智谱/Moonshot/Ollama/vLLM/one-api/new-api 统一接入）；失败/未配置自动降级到 MockProvider</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
